--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,1329 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133715321</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499273</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6785551</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133713867</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>499414</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6785446</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133716044</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>499271</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6785590</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133715765</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499119</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6785540</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133713543</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58291</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499431</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6785417</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133715615</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499216</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6785518</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133713786</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499414</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6785446</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133714902</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499349</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6785501</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133714491</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58117</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499397</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6785483</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133715610</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499216</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6785518</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133713917</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>499414</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6785446</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133715711</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>499156</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6785520</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133715524</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>499225</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6785514</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133714949</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>133715765</v>
       </c>
       <c r="B8" t="n">
-        <v>91939</v>
+        <v>91941</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133715615</v>
+        <v>133713786</v>
       </c>
       <c r="B10" t="n">
         <v>57955</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499216</v>
+        <v>499414</v>
       </c>
       <c r="R10" t="n">
-        <v>6785518</v>
+        <v>6785446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133713786</v>
+        <v>133715615</v>
       </c>
       <c r="B11" t="n">
         <v>57955</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499414</v>
+        <v>499216</v>
       </c>
       <c r="R11" t="n">
-        <v>6785446</v>
+        <v>6785518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
         <v>133714902</v>
       </c>
       <c r="B12" t="n">
-        <v>91939</v>
+        <v>91941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>133715610</v>
       </c>
       <c r="B14" t="n">
-        <v>91939</v>
+        <v>91941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,38 +2130,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133715711</v>
+        <v>133715524</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499156</v>
+        <v>499225</v>
       </c>
       <c r="R16" t="n">
-        <v>6785520</v>
+        <v>6785514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2232,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133715524</v>
+        <v>133715711</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499225</v>
+        <v>499156</v>
       </c>
       <c r="R17" t="n">
-        <v>6785514</v>
+        <v>6785520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -2130,38 +2130,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133715524</v>
+        <v>133715711</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499225</v>
+        <v>499156</v>
       </c>
       <c r="R16" t="n">
-        <v>6785514</v>
+        <v>6785520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2232,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133715711</v>
+        <v>133715524</v>
       </c>
       <c r="B17" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499156</v>
+        <v>499225</v>
       </c>
       <c r="R17" t="n">
-        <v>6785520</v>
+        <v>6785514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>133715765</v>
       </c>
       <c r="B8" t="n">
-        <v>91941</v>
+        <v>91947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>133714902</v>
       </c>
       <c r="B12" t="n">
-        <v>91941</v>
+        <v>91947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>133715610</v>
       </c>
       <c r="B14" t="n">
-        <v>91941</v>
+        <v>91947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,38 +2130,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133715711</v>
+        <v>133715524</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499156</v>
+        <v>499225</v>
       </c>
       <c r="R16" t="n">
-        <v>6785520</v>
+        <v>6785514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2232,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133715524</v>
+        <v>133715711</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499225</v>
+        <v>499156</v>
       </c>
       <c r="R17" t="n">
-        <v>6785514</v>
+        <v>6785520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>133715765</v>
       </c>
       <c r="B8" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>133714902</v>
       </c>
       <c r="B12" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>133715610</v>
       </c>
       <c r="B14" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133716025</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133715141</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133714949</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133715321</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>133713867</v>
       </c>
       <c r="B6" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>133716044</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>133715765</v>
       </c>
       <c r="B8" t="n">
-        <v>91949</v>
+        <v>91968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>133713543</v>
       </c>
       <c r="B9" t="n">
-        <v>58291</v>
+        <v>58298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133713786</v>
+        <v>133715615</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499414</v>
+        <v>499216</v>
       </c>
       <c r="R10" t="n">
-        <v>6785446</v>
+        <v>6785518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133715615</v>
+        <v>133713786</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499216</v>
+        <v>499414</v>
       </c>
       <c r="R11" t="n">
-        <v>6785518</v>
+        <v>6785446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
         <v>133714902</v>
       </c>
       <c r="B12" t="n">
-        <v>91949</v>
+        <v>91968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>133714491</v>
       </c>
       <c r="B13" t="n">
-        <v>58117</v>
+        <v>58124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>133715610</v>
       </c>
       <c r="B14" t="n">
-        <v>91949</v>
+        <v>91968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>133713917</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>133715711</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>133715524</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -1520,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133715615</v>
+        <v>133713786</v>
       </c>
       <c r="B10" t="n">
         <v>57962</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499216</v>
+        <v>499414</v>
       </c>
       <c r="R10" t="n">
-        <v>6785518</v>
+        <v>6785446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133713786</v>
+        <v>133715615</v>
       </c>
       <c r="B11" t="n">
         <v>57962</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499414</v>
+        <v>499216</v>
       </c>
       <c r="R11" t="n">
-        <v>6785446</v>
+        <v>6785518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133714949</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>133715765</v>
       </c>
       <c r="B8" t="n">
-        <v>91968</v>
+        <v>91978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>133713543</v>
       </c>
       <c r="B9" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>133713786</v>
       </c>
       <c r="B10" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>133715615</v>
       </c>
       <c r="B11" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>133714902</v>
       </c>
       <c r="B12" t="n">
-        <v>91968</v>
+        <v>91978</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>133714491</v>
       </c>
       <c r="B13" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>133715610</v>
       </c>
       <c r="B14" t="n">
-        <v>91968</v>
+        <v>91978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>133713917</v>
       </c>
       <c r="B15" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>133715524</v>
       </c>
       <c r="B17" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -1520,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133713786</v>
+        <v>133715615</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499414</v>
+        <v>499216</v>
       </c>
       <c r="R10" t="n">
-        <v>6785446</v>
+        <v>6785518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133715615</v>
+        <v>133713786</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499216</v>
+        <v>499414</v>
       </c>
       <c r="R11" t="n">
-        <v>6785518</v>
+        <v>6785446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -2130,38 +2130,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133715711</v>
+        <v>133715524</v>
       </c>
       <c r="B16" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499156</v>
+        <v>499225</v>
       </c>
       <c r="R16" t="n">
-        <v>6785520</v>
+        <v>6785514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2232,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133715524</v>
+        <v>133715711</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499225</v>
+        <v>499156</v>
       </c>
       <c r="R17" t="n">
-        <v>6785514</v>
+        <v>6785520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -1520,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133715615</v>
+        <v>133713786</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499216</v>
+        <v>499414</v>
       </c>
       <c r="R10" t="n">
-        <v>6785518</v>
+        <v>6785446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133713786</v>
+        <v>133715615</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499414</v>
+        <v>499216</v>
       </c>
       <c r="R11" t="n">
-        <v>6785446</v>
+        <v>6785518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133714949</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>133715765</v>
       </c>
       <c r="B8" t="n">
-        <v>91978</v>
+        <v>91980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>133714902</v>
       </c>
       <c r="B12" t="n">
-        <v>91978</v>
+        <v>91980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>133715610</v>
       </c>
       <c r="B14" t="n">
-        <v>91978</v>
+        <v>91980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -2130,38 +2130,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133715524</v>
+        <v>133715711</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499225</v>
+        <v>499156</v>
       </c>
       <c r="R16" t="n">
-        <v>6785514</v>
+        <v>6785520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2232,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133715711</v>
+        <v>133715524</v>
       </c>
       <c r="B17" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499156</v>
+        <v>499225</v>
       </c>
       <c r="R17" t="n">
-        <v>6785520</v>
+        <v>6785514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -1520,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133715615</v>
+        <v>133713786</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499216</v>
+        <v>499414</v>
       </c>
       <c r="R10" t="n">
-        <v>6785518</v>
+        <v>6785446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133713786</v>
+        <v>133715615</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499414</v>
+        <v>499216</v>
       </c>
       <c r="R11" t="n">
-        <v>6785446</v>
+        <v>6785518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2130,38 +2130,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133715711</v>
+        <v>133715524</v>
       </c>
       <c r="B16" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499156</v>
+        <v>499225</v>
       </c>
       <c r="R16" t="n">
-        <v>6785520</v>
+        <v>6785514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2232,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133715524</v>
+        <v>133715711</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499225</v>
+        <v>499156</v>
       </c>
       <c r="R17" t="n">
-        <v>6785514</v>
+        <v>6785520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133714949</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>133715765</v>
       </c>
       <c r="B8" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>133714902</v>
       </c>
       <c r="B12" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>133715610</v>
       </c>
       <c r="B14" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133716025</v>
+        <v>133714902</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vasseln, Vasseln, Dlr</t>
+          <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499259</v>
+        <v>499349</v>
       </c>
       <c r="R2" t="n">
-        <v>6785581</v>
+        <v>6785501</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,26 +747,16 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -775,65 +764,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133715141</v>
+        <v>133715610</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vasseln, Vasseln, Dlr</t>
+          <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499338</v>
+        <v>499216</v>
       </c>
       <c r="R3" t="n">
-        <v>6785511</v>
+        <v>6785518</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +848,9 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133714949</v>
+        <v>133715765</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +888,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vasseln, Vasseln, Dlr</t>
+          <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499338</v>
+        <v>499119</v>
       </c>
       <c r="R4" t="n">
-        <v>6785511</v>
+        <v>6785540</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,24 +949,9 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +966,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133715321</v>
+        <v>133714949</v>
       </c>
       <c r="B5" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vasseln, Dlr</t>
+          <t>Vasseln, Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499273</v>
+        <v>499338</v>
       </c>
       <c r="R5" t="n">
-        <v>6785551</v>
+        <v>6785511</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,9 +1046,24 @@
           <t>2026-05-22</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,62 +1078,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133713867</v>
+        <v>133716098</v>
       </c>
       <c r="B6" t="n">
-        <v>5181</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499414</v>
+        <v>499268</v>
       </c>
       <c r="R6" t="n">
-        <v>6785446</v>
+        <v>6785611</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,50 +1187,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133716044</v>
+        <v>133716494</v>
       </c>
       <c r="B7" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499271</v>
+        <v>499357</v>
       </c>
       <c r="R7" t="n">
-        <v>6785590</v>
+        <v>6785509</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,37 +1284,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133715765</v>
+        <v>133713680</v>
       </c>
       <c r="B8" t="n">
-        <v>91988</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1356,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499119</v>
+        <v>499402</v>
       </c>
       <c r="R8" t="n">
-        <v>6785540</v>
+        <v>6785429</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,27 +1386,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133713543</v>
+        <v>133713786</v>
       </c>
       <c r="B9" t="n">
-        <v>58308</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1449,7 +1417,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,13 +1426,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499431</v>
+        <v>499414</v>
       </c>
       <c r="R9" t="n">
-        <v>6785417</v>
+        <v>6785446</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,14 +1488,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133713786</v>
+        <v>133713977</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1556,17 +1524,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vasseln, Dlr</t>
+          <t>Vasseln, Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499414</v>
+        <v>499402</v>
       </c>
       <c r="R10" t="n">
-        <v>6785446</v>
+        <v>6785441</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,9 +1561,19 @@
           <t>2026-05-22</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,26 +1588,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133715615</v>
+        <v>133715165</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1662,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499216</v>
+        <v>499306</v>
       </c>
       <c r="R11" t="n">
-        <v>6785518</v>
+        <v>6785523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,52 +1702,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133714902</v>
+        <v>133715349</v>
       </c>
       <c r="B12" t="n">
-        <v>91988</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vasseln, Dlr</t>
+          <t>Vasseln, Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499349</v>
+        <v>499300</v>
       </c>
       <c r="R12" t="n">
-        <v>6785501</v>
+        <v>6785541</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,9 +1775,19 @@
           <t>2026-05-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1813,39 +1802,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133714491</v>
+        <v>133715524</v>
       </c>
       <c r="B13" t="n">
-        <v>58134</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1856,7 +1845,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1865,13 +1854,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499397</v>
+        <v>499225</v>
       </c>
       <c r="R13" t="n">
-        <v>6785483</v>
+        <v>6785514</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,37 +1916,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133715610</v>
+        <v>133715615</v>
       </c>
       <c r="B14" t="n">
-        <v>91988</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2130,38 +2120,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133715524</v>
+        <v>133713867</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>5181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499225</v>
+        <v>499414</v>
       </c>
       <c r="R16" t="n">
-        <v>6785514</v>
+        <v>6785446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2222,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133715711</v>
+        <v>133714399</v>
       </c>
       <c r="B17" t="n">
-        <v>8460</v>
+        <v>58231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>102980</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,13 +2262,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499156</v>
+        <v>499397</v>
       </c>
       <c r="R17" t="n">
-        <v>6785520</v>
+        <v>6785483</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2331,6 +2321,1163 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133713543</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58308</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>499431</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6785417</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133714491</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499397</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6785483</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133714412</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499397</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6785483</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133715141</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499338</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6785511</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133715321</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>499273</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6785551</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133715666</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>499300</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6785541</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133715711</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>499156</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6785520</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133715945</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>499224</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6785551</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133716025</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499259</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6785581</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133716044</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>499271</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6785590</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133716389</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>499360</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6785520</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 51305-2023 artfynd.xlsx
+++ b/artfynd/A 51305-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133714902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715610</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715765</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133714949</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716098</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716494</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713680</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713786</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713977</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715165</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715349</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,6 +1973,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715524</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715615</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713917</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713867</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133714399</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713543</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2525,6 +2615,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133714491</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2627,6 +2722,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133714412</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2739,6 +2839,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715141</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2841,6 +2946,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715321</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2953,6 +3063,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715666</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3055,6 +3170,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715711</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3157,6 +3277,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715945</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3269,6 +3394,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3371,6 +3501,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716044</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3478,8 +3613,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716389</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>